--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2437" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2139" uniqueCount="449">
   <si>
     <t>Property</t>
   </si>
@@ -470,6 +470,19 @@
   <si>
     <t xml:space="preserve">ele-1
 </t>
+  </si>
+  <si>
+    <t>MedicationDispense.extension:rpNumber</t>
+  </si>
+  <si>
+    <t>rpNumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDispense_RpNumber}
+</t>
+  </si>
+  <si>
+    <t>Rp番号</t>
   </si>
   <si>
     <t>MedicationDispense.modifierExtension</t>
@@ -530,22 +543,22 @@
     <t>CombinedMedicationDispense.id</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:rpNumber</t>
-  </si>
-  <si>
-    <t>rpNumber</t>
-  </si>
-  <si>
-    <t>処方箋内部の剤グループとしてのRp番号</t>
-  </si>
-  <si>
-    <t>処方箋内で同一用法の薬剤を慣用的にまとめて、Rpに番号をつけて剤グループとして一括指定されることがある。このスライスでは剤グループに対して割り振られたRp番号を記録する。</t>
-  </si>
-  <si>
-    <t>剤グループに複数の薬剤が含まれる場合、このグループ内の薬剤には同じRp番号が割り振られる。</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:rpNumber.id</t>
+    <t>MedicationDispense.identifier:requestIdentifier</t>
+  </si>
+  <si>
+    <t>requestIdentifier</t>
+  </si>
+  <si>
+    <t>処方オーダに対するID(MedicationRequestからの継承)</t>
+  </si>
+  <si>
+    <t>薬剤をオーダする単位としての処方箋に対するID。原則として調剤の基となったMedicationRequestのIDを設定する。</t>
+  </si>
+  <si>
+    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier.id</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.id</t>
@@ -567,7 +580,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:rpNumber.extension</t>
+    <t>MedicationDispense.identifier:requestIdentifier.extension</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.extension</t>
@@ -585,7 +598,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:rpNumber.use</t>
+    <t>MedicationDispense.identifier:requestIdentifier.use</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.use</t>
@@ -618,7 +631,7 @@
     <t>Role.code or implied by context</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:rpNumber.type</t>
+    <t>MedicationDispense.identifier:requestIdentifier.type</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.type</t>
@@ -655,16 +668,16 @@
     <t>CX.5</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:rpNumber.system</t>
+    <t>MedicationDispense.identifier:requestIdentifier.system</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.system</t>
   </si>
   <si>
-    <t>Rp番号(剤グループ番号)についてのsystem値</t>
-  </si>
-  <si>
-    <t>ここで付番されたIDがRp番号であることを明示するためにOIDとして定義された。urn:oid:1.2.392.100495.20.3.81で固定される。</t>
+    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
     <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
@@ -673,7 +686,7 @@
     <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.100495.20.3.81</t>
+    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -685,19 +698,19 @@
     <t>CX.4 / EI-2-4</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:rpNumber.value</t>
+    <t>MedicationDispense.identifier:requestIdentifier.value</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.value</t>
   </si>
   <si>
-    <t>Rp番号(剤グループ番号)</t>
-  </si>
-  <si>
-    <t>Rp番号(剤グループ番号)。"1"など。</t>
-  </si>
-  <si>
-    <t>value は string型であり、数値はゼロサプレス、つまり、'01'でなく'1'と指定すること。</t>
+    <t>一意の値 / The value that is unique</t>
+  </si>
+  <si>
+    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>Identifier.value</t>
@@ -709,7 +722,7 @@
     <t>CX.1 / EI.1</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:rpNumber.period</t>
+    <t>MedicationDispense.identifier:requestIdentifier.period</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.period</t>
@@ -734,7 +747,7 @@
     <t>CX.7 + CX.8</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:rpNumber.assigner</t>
+    <t>MedicationDispense.identifier:requestIdentifier.assigner</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.assigner</t>
@@ -760,63 +773,6 @@
   </si>
   <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier</t>
-  </si>
-  <si>
-    <t>requestIdentifier</t>
-  </si>
-  <si>
-    <t>処方オーダに対するID(MedicationRequestからの継承)</t>
-  </si>
-  <si>
-    <t>薬剤をオーダする単位としての処方箋に対するID。原則として調剤の基となったMedicationRequestのIDを設定する。</t>
-  </si>
-  <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier.id</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier.extension</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier.use</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier.type</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier.system</t>
-  </si>
-  <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier.value</t>
-  </si>
-  <si>
-    <t>一意の値 / The value that is unique</t>
-  </si>
-  <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier.period</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier.assigner</t>
   </si>
   <si>
     <t>MedicationDispense.partOf</t>
@@ -1781,7 +1737,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO65"/>
+  <dimension ref="A1:AO57"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.73046875" customWidth="true" bestFit="true"/>
@@ -3001,43 +2957,41 @@
         <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="D11" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="N11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>152</v>
-      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>79</v>
       </c>
@@ -3085,7 +3039,7 @@
         <v>79</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3094,7 +3048,7 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>140</v>
@@ -3103,7 +3057,7 @@
         <v>79</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>79</v>
@@ -3117,18 +3071,18 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>81</v>
@@ -3137,24 +3091,26 @@
         <v>79</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N12" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="O12" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="M12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>79</v>
       </c>
@@ -3190,17 +3146,19 @@
         <v>79</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="AC12" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3212,19 +3170,19 @@
         <v>79</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>160</v>
+        <v>79</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>161</v>
+        <v>132</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>162</v>
+        <v>79</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>79</v>
@@ -3232,23 +3190,21 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>79</v>
@@ -3260,16 +3216,16 @@
         <v>79</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3307,19 +3263,17 @@
         <v>79</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="AC13" s="2"/>
       <c r="AD13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3334,16 +3288,16 @@
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>79</v>
@@ -3351,12 +3305,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="C14" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="B14" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>79</v>
       </c>
@@ -3365,7 +3321,7 @@
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>79</v>
@@ -3377,15 +3333,17 @@
         <v>79</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="M14" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>79</v>
@@ -3434,31 +3392,31 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>79</v>
+        <v>164</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>79</v>
+        <v>166</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>79</v>
+        <v>167</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>79</v>
@@ -3466,21 +3424,21 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>79</v>
@@ -3492,17 +3450,15 @@
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>79</v>
@@ -3539,37 +3495,37 @@
         <v>79</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>180</v>
+        <v>79</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>79</v>
@@ -3583,46 +3539,44 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>79</v>
       </c>
@@ -3646,49 +3600,49 @@
         <v>79</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>188</v>
+        <v>79</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>190</v>
+        <v>79</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>79</v>
+        <v>184</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>79</v>
@@ -3697,15 +3651,15 @@
         <v>79</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3722,25 +3676,25 @@
         <v>79</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>195</v>
+        <v>109</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>79</v>
@@ -3765,13 +3719,13 @@
         <v>79</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>79</v>
@@ -3789,7 +3743,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3807,7 +3761,7 @@
         <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>79</v>
@@ -3816,15 +3770,15 @@
         <v>79</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>204</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3832,7 +3786,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>89</v>
@@ -3847,26 +3801,26 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>103</v>
+        <v>199</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>211</v>
+        <v>79</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>79</v>
@@ -3884,13 +3838,13 @@
         <v>79</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>79</v>
+        <v>205</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>79</v>
+        <v>206</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>79</v>
@@ -3908,7 +3862,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3926,7 +3880,7 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>79</v>
@@ -3935,15 +3889,15 @@
         <v>79</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3966,24 +3920,26 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>171</v>
+        <v>103</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O19" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>79</v>
+        <v>215</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>79</v>
@@ -4025,7 +3981,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4043,7 +3999,7 @@
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>79</v>
@@ -4052,15 +4008,15 @@
         <v>79</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4068,7 +4024,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>89</v>
@@ -4083,15 +4039,17 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>225</v>
+        <v>175</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -4140,7 +4098,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4158,7 +4116,7 @@
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
@@ -4167,15 +4125,15 @@
         <v>79</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4198,17 +4156,15 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -4257,7 +4213,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4275,7 +4231,7 @@
         <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>79</v>
@@ -4284,19 +4240,17 @@
         <v>79</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>79</v>
       </c>
@@ -4305,7 +4259,7 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>79</v>
@@ -4314,19 +4268,19 @@
         <v>79</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>155</v>
+        <v>237</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4376,13 +4330,13 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>154</v>
+        <v>241</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>79</v>
@@ -4391,27 +4345,27 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>160</v>
+        <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>161</v>
+        <v>242</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>162</v>
+        <v>79</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>79</v>
+        <v>243</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>170</v>
+        <v>244</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4422,7 +4376,7 @@
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>79</v>
@@ -4434,13 +4388,13 @@
         <v>79</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>171</v>
+        <v>245</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>172</v>
+        <v>246</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>173</v>
+        <v>247</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4491,25 +4445,25 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>174</v>
+        <v>244</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>79</v>
+        <v>248</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>175</v>
+        <v>249</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>79</v>
@@ -4523,42 +4477,42 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>177</v>
+        <v>250</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>178</v>
+        <v>251</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>179</v>
+        <v>252</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>151</v>
+        <v>253</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4584,55 +4538,55 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>79</v>
+        <v>192</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>79</v>
+        <v>254</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>79</v>
+        <v>255</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>180</v>
+        <v>79</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>181</v>
+        <v>250</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>79</v>
+        <v>256</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>175</v>
+        <v>257</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>79</v>
+        <v>258</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>79</v>
+        <v>259</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>79</v>
@@ -4640,10 +4594,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>183</v>
+        <v>260</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4660,26 +4614,22 @@
         <v>79</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>109</v>
+        <v>261</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>184</v>
+        <v>262</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>79</v>
       </c>
@@ -4703,13 +4653,13 @@
         <v>79</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>188</v>
+        <v>264</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>189</v>
+        <v>265</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>190</v>
+        <v>266</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>79</v>
@@ -4727,7 +4677,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>191</v>
+        <v>260</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4742,10 +4692,10 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>79</v>
+        <v>267</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>192</v>
+        <v>268</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>79</v>
@@ -4754,15 +4704,15 @@
         <v>79</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>194</v>
+        <v>269</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4782,23 +4732,21 @@
         <v>79</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>196</v>
+        <v>270</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>197</v>
+        <v>271</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>79</v>
       </c>
@@ -4822,13 +4770,13 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>200</v>
+        <v>113</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>201</v>
+        <v>273</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>202</v>
+        <v>274</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
@@ -4846,7 +4794,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>203</v>
+        <v>269</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4864,7 +4812,7 @@
         <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>192</v>
+        <v>275</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>79</v>
@@ -4873,15 +4821,15 @@
         <v>79</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>204</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>249</v>
+        <v>276</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>206</v>
+        <v>276</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4904,26 +4852,24 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>103</v>
+        <v>277</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>250</v>
+        <v>278</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>252</v>
+        <v>79</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>79</v>
@@ -4965,10 +4911,10 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>212</v>
+        <v>276</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>89</v>
@@ -4980,27 +4926,27 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>79</v>
+        <v>281</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>213</v>
+        <v>282</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>79</v>
+        <v>284</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>214</v>
+        <v>285</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>253</v>
+        <v>286</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>216</v>
+        <v>286</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5023,16 +4969,16 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>171</v>
+        <v>287</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>254</v>
+        <v>288</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>255</v>
+        <v>289</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>256</v>
+        <v>290</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5082,7 +5028,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>220</v>
+        <v>286</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5097,27 +5043,27 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>79</v>
+        <v>291</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>221</v>
+        <v>292</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>79</v>
+        <v>293</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>222</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>257</v>
+        <v>295</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>224</v>
+        <v>295</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5137,18 +5083,20 @@
         <v>79</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>225</v>
+        <v>296</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>226</v>
+        <v>297</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5197,7 +5145,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5212,10 +5160,10 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>79</v>
+        <v>299</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>229</v>
+        <v>300</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>79</v>
@@ -5224,15 +5172,15 @@
         <v>79</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>230</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>258</v>
+        <v>301</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>232</v>
+        <v>301</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5243,7 +5191,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>79</v>
@@ -5252,19 +5200,19 @@
         <v>79</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>233</v>
+        <v>302</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>234</v>
+        <v>303</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>235</v>
+        <v>304</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>236</v>
+        <v>290</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5314,13 +5262,13 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>237</v>
+        <v>301</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>79</v>
@@ -5332,24 +5280,24 @@
         <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>238</v>
+        <v>305</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>79</v>
+        <v>306</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>239</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>259</v>
+        <v>307</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>259</v>
+        <v>307</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5372,13 +5320,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>260</v>
+        <v>308</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>261</v>
+        <v>309</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>262</v>
+        <v>310</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5429,7 +5377,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>259</v>
+        <v>307</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5444,10 +5392,10 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>264</v>
+        <v>312</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>79</v>
@@ -5461,10 +5409,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>265</v>
+        <v>313</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>265</v>
+        <v>313</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5472,7 +5420,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>89</v>
@@ -5481,23 +5429,21 @@
         <v>79</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>109</v>
+        <v>175</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>266</v>
+        <v>176</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>79</v>
@@ -5522,13 +5468,13 @@
         <v>79</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>188</v>
+        <v>79</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>269</v>
+        <v>79</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>270</v>
+        <v>79</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>79</v>
@@ -5546,10 +5492,10 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>265</v>
+        <v>178</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>89</v>
@@ -5558,19 +5504,19 @@
         <v>79</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>271</v>
+        <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>272</v>
+        <v>179</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>273</v>
+        <v>79</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>274</v>
+        <v>79</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -5578,21 +5524,21 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>275</v>
+        <v>314</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>275</v>
+        <v>314</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>79</v>
@@ -5604,15 +5550,17 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>276</v>
+        <v>134</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>277</v>
+        <v>182</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -5637,13 +5585,13 @@
         <v>79</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>279</v>
+        <v>79</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>280</v>
+        <v>79</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>281</v>
+        <v>79</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>79</v>
@@ -5661,25 +5609,25 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>275</v>
+        <v>185</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>282</v>
+        <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>283</v>
+        <v>179</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>79</v>
@@ -5693,44 +5641,46 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>284</v>
+        <v>315</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>284</v>
+        <v>315</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>79</v>
+        <v>316</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>195</v>
+        <v>134</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>285</v>
+        <v>317</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>286</v>
+        <v>318</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
       </c>
@@ -5754,13 +5704,13 @@
         <v>79</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>288</v>
+        <v>79</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>289</v>
+        <v>79</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>79</v>
@@ -5778,25 +5728,25 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>284</v>
+        <v>319</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>290</v>
+        <v>132</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>79</v>
@@ -5810,10 +5760,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>291</v>
+        <v>320</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>291</v>
+        <v>320</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5821,7 +5771,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>89</v>
@@ -5833,21 +5783,21 @@
         <v>79</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>292</v>
+        <v>199</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>293</v>
+        <v>321</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>79</v>
       </c>
@@ -5871,13 +5821,13 @@
         <v>79</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>79</v>
+        <v>264</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>79</v>
+        <v>324</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>79</v>
+        <v>325</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>79</v>
@@ -5895,10 +5845,10 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>291</v>
+        <v>320</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>89</v>
@@ -5910,27 +5860,27 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>296</v>
+        <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>297</v>
+        <v>326</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>298</v>
+        <v>79</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>299</v>
+        <v>79</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>300</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>301</v>
+        <v>327</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>301</v>
+        <v>327</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5950,20 +5900,18 @@
         <v>79</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>79</v>
@@ -6012,10 +5960,10 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>301</v>
+        <v>327</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>89</v>
@@ -6027,27 +5975,27 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>307</v>
+        <v>332</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>308</v>
+        <v>79</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>309</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6070,16 +6018,16 @@
         <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>311</v>
+        <v>334</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6129,7 +6077,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6144,10 +6092,10 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>314</v>
+        <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>315</v>
+        <v>337</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>79</v>
@@ -6161,10 +6109,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6187,16 +6135,16 @@
         <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>305</v>
+        <v>342</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6246,7 +6194,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6261,27 +6209,27 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>79</v>
+        <v>343</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>320</v>
+        <v>344</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>321</v>
+        <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>79</v>
+        <v>345</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>79</v>
+        <v>346</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6292,7 +6240,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>79</v>
@@ -6304,15 +6252,17 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>323</v>
+        <v>199</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>324</v>
+        <v>348</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6337,13 +6287,13 @@
         <v>79</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>79</v>
+        <v>264</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>79</v>
+        <v>351</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>79</v>
+        <v>352</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>79</v>
@@ -6361,13 +6311,13 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>79</v>
@@ -6376,27 +6326,27 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>326</v>
+        <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>327</v>
+        <v>353</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>79</v>
+        <v>354</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>79</v>
+        <v>355</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6404,7 +6354,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>89</v>
@@ -6419,15 +6369,17 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>171</v>
+        <v>357</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>172</v>
+        <v>358</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>79</v>
@@ -6476,7 +6428,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>174</v>
+        <v>356</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6485,16 +6437,16 @@
         <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>79</v>
+        <v>361</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>175</v>
+        <v>362</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>79</v>
@@ -6503,26 +6455,26 @@
         <v>79</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>79</v>
+        <v>363</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>329</v>
+        <v>364</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>329</v>
+        <v>364</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>79</v>
@@ -6534,16 +6486,16 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>134</v>
+        <v>357</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>178</v>
+        <v>365</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>179</v>
+        <v>366</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>151</v>
+        <v>360</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6593,25 +6545,25 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>181</v>
+        <v>364</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>140</v>
+        <v>361</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>175</v>
+        <v>362</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>79</v>
@@ -6620,51 +6572,47 @@
         <v>79</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>79</v>
+        <v>363</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>330</v>
+        <v>367</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>330</v>
+        <v>367</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>331</v>
+        <v>79</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J42" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>134</v>
+        <v>368</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>332</v>
+        <v>369</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>79</v>
       </c>
@@ -6712,42 +6660,42 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>334</v>
+        <v>367</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>132</v>
+        <v>370</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>79</v>
+        <v>371</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>79</v>
+        <v>372</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>335</v>
+        <v>373</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>335</v>
+        <v>373</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6755,7 +6703,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>89</v>
@@ -6770,18 +6718,16 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>195</v>
+        <v>368</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>336</v>
+        <v>374</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>337</v>
+        <v>375</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>338</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>79</v>
       </c>
@@ -6805,13 +6751,13 @@
         <v>79</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>279</v>
+        <v>79</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>339</v>
+        <v>79</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>340</v>
+        <v>79</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>79</v>
@@ -6829,7 +6775,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>335</v>
+        <v>373</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6844,27 +6790,27 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>79</v>
+        <v>376</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>341</v>
+        <v>377</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>79</v>
+        <v>371</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>79</v>
+        <v>372</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>342</v>
+        <v>378</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>342</v>
+        <v>378</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6872,7 +6818,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>89</v>
@@ -6887,15 +6833,17 @@
         <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>344</v>
+        <v>379</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6944,10 +6892,10 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>342</v>
+        <v>378</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>89</v>
@@ -6959,27 +6907,27 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>346</v>
+        <v>79</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>347</v>
+        <v>381</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>79</v>
+        <v>382</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>79</v>
+        <v>383</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>348</v>
+        <v>384</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>348</v>
+        <v>384</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6990,7 +6938,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>79</v>
@@ -7002,16 +6950,16 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>349</v>
+        <v>385</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>350</v>
+        <v>386</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>351</v>
+        <v>387</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7061,13 +7009,13 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>348</v>
+        <v>384</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>79</v>
@@ -7079,13 +7027,13 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>352</v>
+        <v>388</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>79</v>
+        <v>389</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7093,10 +7041,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>353</v>
+        <v>390</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>353</v>
+        <v>390</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7119,16 +7067,16 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>354</v>
+        <v>391</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>355</v>
+        <v>392</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>356</v>
+        <v>393</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>357</v>
+        <v>394</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7178,7 +7126,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>353</v>
+        <v>390</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7193,27 +7141,27 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>358</v>
+        <v>395</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>359</v>
+        <v>396</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>360</v>
+        <v>79</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>361</v>
+        <v>397</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>362</v>
+        <v>398</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>362</v>
+        <v>398</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7224,7 +7172,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>79</v>
@@ -7236,16 +7184,16 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>195</v>
+        <v>399</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>363</v>
+        <v>400</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>364</v>
+        <v>400</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>365</v>
+        <v>401</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7271,13 +7219,13 @@
         <v>79</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>279</v>
+        <v>79</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>366</v>
+        <v>79</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>367</v>
+        <v>79</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>79</v>
@@ -7295,13 +7243,13 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>362</v>
+        <v>398</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>79</v>
@@ -7313,24 +7261,24 @@
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>368</v>
+        <v>402</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>369</v>
+        <v>79</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>370</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7338,7 +7286,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>89</v>
@@ -7353,17 +7301,15 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>372</v>
+        <v>308</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>373</v>
+        <v>404</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7412,7 +7358,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7421,33 +7367,33 @@
         <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>376</v>
+        <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>79</v>
+        <v>407</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>378</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>379</v>
+        <v>408</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>379</v>
+        <v>408</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7470,17 +7416,15 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>372</v>
+        <v>175</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>380</v>
+        <v>176</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>79</v>
@@ -7529,7 +7473,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>379</v>
+        <v>178</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7538,16 +7482,16 @@
         <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>376</v>
+        <v>79</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>377</v>
+        <v>179</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
@@ -7556,26 +7500,26 @@
         <v>79</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>378</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>382</v>
+        <v>409</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>382</v>
+        <v>409</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>79</v>
@@ -7584,18 +7528,20 @@
         <v>79</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>383</v>
+        <v>134</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>384</v>
+        <v>182</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -7644,74 +7590,78 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>382</v>
+        <v>185</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>385</v>
+        <v>179</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>386</v>
+        <v>79</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>387</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>388</v>
+        <v>410</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>388</v>
+        <v>410</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>79</v>
+        <v>316</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>383</v>
+        <v>134</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>389</v>
+        <v>317</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
       </c>
@@ -7759,42 +7709,42 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>388</v>
+        <v>319</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>391</v>
+        <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>392</v>
+        <v>132</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>386</v>
+        <v>79</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>387</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7802,7 +7752,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>89</v>
@@ -7817,17 +7767,15 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>349</v>
+        <v>412</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -7876,10 +7824,10 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>89</v>
@@ -7894,24 +7842,24 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>397</v>
+        <v>79</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>398</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>399</v>
+        <v>416</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>399</v>
+        <v>416</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7922,7 +7870,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>79</v>
@@ -7934,17 +7882,15 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>400</v>
+        <v>199</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -7969,13 +7915,13 @@
         <v>79</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>79</v>
+        <v>264</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>79</v>
+        <v>419</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>79</v>
+        <v>420</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>79</v>
@@ -7993,13 +7939,13 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>399</v>
+        <v>416</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>79</v>
@@ -8011,24 +7957,24 @@
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>403</v>
+        <v>353</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>404</v>
+        <v>421</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>79</v>
+        <v>422</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8051,17 +7997,15 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>406</v>
+        <v>199</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>407</v>
+        <v>424</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>409</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8086,13 +8030,13 @@
         <v>79</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>79</v>
+        <v>264</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>79</v>
+        <v>426</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>79</v>
+        <v>427</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>79</v>
@@ -8110,7 +8054,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8125,27 +8069,27 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>410</v>
+        <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>411</v>
+        <v>428</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>79</v>
+        <v>429</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>412</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8168,16 +8112,16 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>416</v>
+        <v>290</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8227,7 +8171,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8245,13 +8189,13 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>417</v>
+        <v>434</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>79</v>
+        <v>435</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
@@ -8259,21 +8203,21 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>79</v>
+        <v>437</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>79</v>
@@ -8285,15 +8229,17 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>323</v>
+        <v>438</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>419</v>
+        <v>439</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>79</v>
@@ -8342,13 +8288,13 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>79</v>
@@ -8360,13 +8306,13 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>421</v>
+        <v>442</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>422</v>
+        <v>79</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>79</v>
@@ -8374,10 +8320,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>423</v>
+        <v>443</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>423</v>
+        <v>443</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8388,7 +8334,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>79</v>
@@ -8400,15 +8346,17 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>171</v>
+        <v>444</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>172</v>
+        <v>445</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>446</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>447</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>79</v>
@@ -8457,25 +8405,25 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>174</v>
+        <v>443</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>175</v>
+        <v>448</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>79</v>
@@ -8484,938 +8432,6 @@
         <v>79</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O58" s="2"/>
-      <c r="P58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="P59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
-      <c r="P60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
-      <c r="P61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
-      <c r="P62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O63" s="2"/>
-      <c r="P63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="O64" s="2"/>
-      <c r="P64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="O65" s="2"/>
-      <c r="P65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO65" t="s" s="2">
         <v>79</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2139" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2437" uniqueCount="464">
   <si>
     <t>Property</t>
   </si>
@@ -470,19 +470,6 @@
   <si>
     <t xml:space="preserve">ele-1
 </t>
-  </si>
-  <si>
-    <t>MedicationDispense.extension:rpNumber</t>
-  </si>
-  <si>
-    <t>rpNumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDispense_RpNumber}
-</t>
-  </si>
-  <si>
-    <t>Rp番号</t>
   </si>
   <si>
     <t>MedicationDispense.modifierExtension</t>
@@ -543,22 +530,22 @@
     <t>CombinedMedicationDispense.id</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:requestIdentifier</t>
-  </si>
-  <si>
-    <t>requestIdentifier</t>
-  </si>
-  <si>
-    <t>処方オーダに対するID(MedicationRequestからの継承)</t>
-  </si>
-  <si>
-    <t>薬剤をオーダする単位としての処方箋に対するID。原則として調剤の基となったMedicationRequestのIDを設定する。</t>
-  </si>
-  <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
-  </si>
-  <si>
-    <t>MedicationDispense.identifier:requestIdentifier.id</t>
+    <t>MedicationDispense.identifier:rpNumber</t>
+  </si>
+  <si>
+    <t>rpNumber</t>
+  </si>
+  <si>
+    <t>処方箋内部の剤グループとしてのRp番号</t>
+  </si>
+  <si>
+    <t>処方箋内で同一用法の薬剤を慣用的にまとめて、Rpに番号をつけて剤グループとして一括指定されることがある。このスライスでは剤グループに対して割り振られたRp番号を記録する。</t>
+  </si>
+  <si>
+    <t>剤グループに複数の薬剤が含まれる場合、このグループ内の薬剤には同じRp番号が割り振られる。</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:rpNumber.id</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.id</t>
@@ -580,7 +567,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:requestIdentifier.extension</t>
+    <t>MedicationDispense.identifier:rpNumber.extension</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.extension</t>
@@ -598,7 +585,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:requestIdentifier.use</t>
+    <t>MedicationDispense.identifier:rpNumber.use</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.use</t>
@@ -631,7 +618,7 @@
     <t>Role.code or implied by context</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:requestIdentifier.type</t>
+    <t>MedicationDispense.identifier:rpNumber.type</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.type</t>
@@ -668,16 +655,16 @@
     <t>CX.5</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:requestIdentifier.system</t>
+    <t>MedicationDispense.identifier:rpNumber.system</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.system</t>
   </si>
   <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+    <t>Rp番号(剤グループ番号)についてのsystem値</t>
+  </si>
+  <si>
+    <t>ここで付番されたIDがRp番号であることを明示するためにOIDとして定義された。urn:oid:1.2.392.100495.20.3.81で固定される。</t>
   </si>
   <si>
     <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
@@ -686,7 +673,7 @@
     <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
+    <t>urn:oid:1.2.392.100495.20.3.81</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -698,19 +685,19 @@
     <t>CX.4 / EI-2-4</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:requestIdentifier.value</t>
+    <t>MedicationDispense.identifier:rpNumber.value</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.value</t>
   </si>
   <si>
-    <t>一意の値 / The value that is unique</t>
-  </si>
-  <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>Rp番号(剤グループ番号)</t>
+  </si>
+  <si>
+    <t>Rp番号(剤グループ番号)。"1"など。</t>
+  </si>
+  <si>
+    <t>value は string型であり、数値はゼロサプレス、つまり、'01'でなく'1'と指定すること。</t>
   </si>
   <si>
     <t>Identifier.value</t>
@@ -722,7 +709,7 @@
     <t>CX.1 / EI.1</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:requestIdentifier.period</t>
+    <t>MedicationDispense.identifier:rpNumber.period</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.period</t>
@@ -747,7 +734,7 @@
     <t>CX.7 + CX.8</t>
   </si>
   <si>
-    <t>MedicationDispense.identifier:requestIdentifier.assigner</t>
+    <t>MedicationDispense.identifier:rpNumber.assigner</t>
   </si>
   <si>
     <t>MedicationDispense.identifier.assigner</t>
@@ -773,6 +760,63 @@
   </si>
   <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier</t>
+  </si>
+  <si>
+    <t>requestIdentifier</t>
+  </si>
+  <si>
+    <t>処方オーダに対するID(MedicationRequestからの継承)</t>
+  </si>
+  <si>
+    <t>薬剤をオーダする単位としての処方箋に対するID。原則として調剤の基となったMedicationRequestのIDを設定する。</t>
+  </si>
+  <si>
+    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier.id</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier.extension</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier.use</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier.type</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier.system</t>
+  </si>
+  <si>
+    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier.value</t>
+  </si>
+  <si>
+    <t>一意の値 / The value that is unique</t>
+  </si>
+  <si>
+    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier.period</t>
+  </si>
+  <si>
+    <t>MedicationDispense.identifier:requestIdentifier.assigner</t>
   </si>
   <si>
     <t>MedicationDispense.partOf</t>
@@ -1737,7 +1781,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO57"/>
+  <dimension ref="A1:AO65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.73046875" customWidth="true" bestFit="true"/>
@@ -2957,41 +3001,43 @@
         <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="C11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
+      <c r="N11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O11" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P11" t="s" s="2">
         <v>79</v>
       </c>
@@ -3039,7 +3085,7 @@
         <v>79</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3048,7 +3094,7 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>140</v>
@@ -3057,7 +3103,7 @@
         <v>79</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>79</v>
@@ -3071,18 +3117,18 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>81</v>
@@ -3091,26 +3137,24 @@
         <v>79</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>79</v>
       </c>
@@ -3146,19 +3190,17 @@
         <v>79</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="AC12" s="2"/>
       <c r="AD12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3170,19 +3212,19 @@
         <v>79</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>79</v>
+        <v>163</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>79</v>
@@ -3190,21 +3232,23 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="D13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>79</v>
@@ -3216,16 +3260,16 @@
         <v>79</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3263,17 +3307,19 @@
         <v>79</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AC13" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3288,16 +3334,16 @@
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>79</v>
@@ -3305,14 +3351,12 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>169</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>79</v>
       </c>
@@ -3321,7 +3365,7 @@
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>79</v>
@@ -3333,17 +3377,15 @@
         <v>79</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>172</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>79</v>
@@ -3392,31 +3434,31 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>167</v>
+        <v>79</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>79</v>
@@ -3424,21 +3466,21 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>79</v>
@@ -3450,15 +3492,17 @@
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>79</v>
@@ -3495,37 +3539,37 @@
         <v>79</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>79</v>
+        <v>180</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>79</v>
@@ -3539,44 +3583,46 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="O16" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>79</v>
       </c>
@@ -3600,49 +3646,49 @@
         <v>79</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>79</v>
+        <v>188</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>79</v>
+        <v>190</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>184</v>
+        <v>79</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>79</v>
@@ -3651,15 +3697,15 @@
         <v>79</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>79</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3676,25 +3722,25 @@
         <v>79</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>109</v>
+        <v>195</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>79</v>
@@ -3719,13 +3765,13 @@
         <v>79</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>79</v>
@@ -3743,7 +3789,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3761,7 +3807,7 @@
         <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>79</v>
@@ -3770,15 +3816,15 @@
         <v>79</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>132</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3786,7 +3832,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>89</v>
@@ -3801,26 +3847,26 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>79</v>
+        <v>211</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>79</v>
@@ -3838,13 +3884,13 @@
         <v>79</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>204</v>
+        <v>79</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>205</v>
+        <v>79</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>206</v>
+        <v>79</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>79</v>
@@ -3862,7 +3908,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3880,7 +3926,7 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>79</v>
@@ -3889,15 +3935,15 @@
         <v>79</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3920,26 +3966,24 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>215</v>
+        <v>79</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>79</v>
@@ -3981,7 +4025,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3999,7 +4043,7 @@
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>79</v>
@@ -4008,15 +4052,15 @@
         <v>79</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4024,7 +4068,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>89</v>
@@ -4039,17 +4083,15 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>175</v>
+        <v>225</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -4098,7 +4140,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4116,7 +4158,7 @@
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
@@ -4125,15 +4167,15 @@
         <v>79</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4156,15 +4198,17 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -4213,7 +4257,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4231,7 +4275,7 @@
         <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>79</v>
@@ -4240,17 +4284,19 @@
         <v>79</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>79</v>
       </c>
@@ -4259,7 +4305,7 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>79</v>
@@ -4268,19 +4314,19 @@
         <v>79</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>237</v>
+        <v>155</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4330,13 +4376,13 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>241</v>
+        <v>154</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>79</v>
@@ -4345,27 +4391,27 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>242</v>
+        <v>161</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>79</v>
+        <v>163</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>243</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>244</v>
+        <v>170</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4376,7 +4422,7 @@
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>79</v>
@@ -4388,13 +4434,13 @@
         <v>79</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>245</v>
+        <v>171</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>246</v>
+        <v>172</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>247</v>
+        <v>173</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4445,25 +4491,25 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>244</v>
+        <v>174</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>248</v>
+        <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>249</v>
+        <v>175</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>79</v>
@@ -4477,42 +4523,42 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>250</v>
+        <v>177</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>251</v>
+        <v>178</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>252</v>
+        <v>179</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>253</v>
+        <v>151</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4538,55 +4584,55 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>192</v>
+        <v>79</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>254</v>
+        <v>79</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>255</v>
+        <v>79</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>79</v>
+        <v>180</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>250</v>
+        <v>181</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>256</v>
+        <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>257</v>
+        <v>175</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>258</v>
+        <v>79</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>259</v>
+        <v>79</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>79</v>
@@ -4594,10 +4640,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>260</v>
+        <v>183</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4614,22 +4660,26 @@
         <v>79</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>261</v>
+        <v>109</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>262</v>
+        <v>184</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>79</v>
       </c>
@@ -4653,13 +4703,13 @@
         <v>79</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>264</v>
+        <v>188</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>265</v>
+        <v>189</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>266</v>
+        <v>190</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>79</v>
@@ -4677,7 +4727,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>260</v>
+        <v>191</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4692,10 +4742,10 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>267</v>
+        <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>268</v>
+        <v>192</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>79</v>
@@ -4704,15 +4754,15 @@
         <v>79</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>79</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>269</v>
+        <v>194</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4732,21 +4782,23 @@
         <v>79</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="O26" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="L26" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>79</v>
       </c>
@@ -4770,13 +4822,13 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>113</v>
+        <v>200</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>273</v>
+        <v>201</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>274</v>
+        <v>202</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
@@ -4794,7 +4846,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>269</v>
+        <v>203</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4812,7 +4864,7 @@
         <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>275</v>
+        <v>192</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>79</v>
@@ -4821,15 +4873,15 @@
         <v>79</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>79</v>
+        <v>204</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>276</v>
+        <v>249</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>276</v>
+        <v>206</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4852,24 +4904,26 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>277</v>
+        <v>103</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>278</v>
+        <v>250</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>79</v>
+        <v>252</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>79</v>
@@ -4911,10 +4965,10 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>276</v>
+        <v>212</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>89</v>
@@ -4926,27 +4980,27 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>281</v>
+        <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>282</v>
+        <v>213</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>283</v>
+        <v>79</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>284</v>
+        <v>79</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>285</v>
+        <v>214</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>286</v>
+        <v>253</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>286</v>
+        <v>216</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4969,16 +5023,16 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>287</v>
+        <v>171</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>288</v>
+        <v>254</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>289</v>
+        <v>255</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5028,7 +5082,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>286</v>
+        <v>220</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5043,27 +5097,27 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>291</v>
+        <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>292</v>
+        <v>221</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>293</v>
+        <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>294</v>
+        <v>222</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>295</v>
+        <v>257</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>295</v>
+        <v>224</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5083,20 +5137,18 @@
         <v>79</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>296</v>
+        <v>225</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>297</v>
+        <v>226</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5145,7 +5197,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>295</v>
+        <v>228</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5160,10 +5212,10 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>299</v>
+        <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>300</v>
+        <v>229</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>79</v>
@@ -5172,15 +5224,15 @@
         <v>79</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>79</v>
+        <v>230</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>301</v>
+        <v>258</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>301</v>
+        <v>232</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5191,7 +5243,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>79</v>
@@ -5200,19 +5252,19 @@
         <v>79</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>302</v>
+        <v>233</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>303</v>
+        <v>234</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>304</v>
+        <v>235</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>290</v>
+        <v>236</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5262,13 +5314,13 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>301</v>
+        <v>237</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>79</v>
@@ -5280,24 +5332,24 @@
         <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>305</v>
+        <v>238</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>306</v>
+        <v>79</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>79</v>
+        <v>239</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>307</v>
+        <v>259</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>307</v>
+        <v>259</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5320,13 +5372,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>308</v>
+        <v>260</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>309</v>
+        <v>261</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>310</v>
+        <v>262</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5377,7 +5429,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>307</v>
+        <v>259</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5392,10 +5444,10 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>311</v>
+        <v>263</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>312</v>
+        <v>264</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>79</v>
@@ -5409,10 +5461,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>313</v>
+        <v>265</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>313</v>
+        <v>265</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5420,7 +5472,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>89</v>
@@ -5429,21 +5481,23 @@
         <v>79</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>175</v>
+        <v>109</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>176</v>
+        <v>266</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>79</v>
@@ -5468,13 +5522,13 @@
         <v>79</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>79</v>
+        <v>188</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>79</v>
+        <v>269</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>79</v>
+        <v>270</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>79</v>
@@ -5492,10 +5546,10 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>178</v>
+        <v>265</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>89</v>
@@ -5504,19 +5558,19 @@
         <v>79</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>79</v>
+        <v>271</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>179</v>
+        <v>272</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>79</v>
+        <v>273</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>79</v>
+        <v>274</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -5524,21 +5578,21 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>314</v>
+        <v>275</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>314</v>
+        <v>275</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>79</v>
@@ -5550,17 +5604,15 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>134</v>
+        <v>276</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>182</v>
+        <v>277</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -5585,13 +5637,13 @@
         <v>79</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>79</v>
+        <v>279</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>79</v>
+        <v>280</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>79</v>
+        <v>281</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>79</v>
@@ -5609,25 +5661,25 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>185</v>
+        <v>275</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>79</v>
+        <v>282</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>179</v>
+        <v>283</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>79</v>
@@ -5641,46 +5693,44 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>315</v>
+        <v>284</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>315</v>
+        <v>284</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>316</v>
+        <v>79</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>134</v>
+        <v>195</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>317</v>
+        <v>285</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>318</v>
+        <v>286</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>79</v>
       </c>
@@ -5704,13 +5754,13 @@
         <v>79</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>79</v>
+        <v>288</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>79</v>
+        <v>289</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>79</v>
@@ -5728,25 +5778,25 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>319</v>
+        <v>284</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>132</v>
+        <v>290</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>79</v>
@@ -5760,10 +5810,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>320</v>
+        <v>291</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>320</v>
+        <v>291</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5771,7 +5821,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>89</v>
@@ -5783,21 +5833,21 @@
         <v>79</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>199</v>
+        <v>292</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>321</v>
+        <v>293</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>79</v>
       </c>
@@ -5821,13 +5871,13 @@
         <v>79</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>264</v>
+        <v>79</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>324</v>
+        <v>79</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>325</v>
+        <v>79</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>79</v>
@@ -5845,10 +5895,10 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>320</v>
+        <v>291</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>89</v>
@@ -5860,27 +5910,27 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>79</v>
+        <v>296</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>79</v>
+        <v>298</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>79</v>
+        <v>299</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>79</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>327</v>
+        <v>301</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>327</v>
+        <v>301</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5900,18 +5950,20 @@
         <v>79</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>328</v>
+        <v>302</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>329</v>
+        <v>303</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>79</v>
@@ -5960,10 +6012,10 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>327</v>
+        <v>301</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>89</v>
@@ -5975,27 +6027,27 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>331</v>
+        <v>306</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>332</v>
+        <v>307</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>79</v>
+        <v>308</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>79</v>
+        <v>309</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>333</v>
+        <v>310</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>333</v>
+        <v>310</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6018,16 +6070,16 @@
         <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>334</v>
+        <v>311</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>335</v>
+        <v>312</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>336</v>
+        <v>313</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6077,7 +6129,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>333</v>
+        <v>310</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6092,10 +6144,10 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>79</v>
+        <v>314</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>337</v>
+        <v>315</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>79</v>
@@ -6109,10 +6161,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6135,16 +6187,16 @@
         <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>339</v>
+        <v>317</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>341</v>
+        <v>319</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>342</v>
+        <v>305</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6194,7 +6246,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6209,27 +6261,27 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>343</v>
+        <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>344</v>
+        <v>320</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>79</v>
+        <v>321</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>345</v>
+        <v>79</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>346</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>347</v>
+        <v>322</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>347</v>
+        <v>322</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6240,7 +6292,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>79</v>
@@ -6252,17 +6304,15 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>199</v>
+        <v>323</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>348</v>
+        <v>324</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6287,13 +6337,13 @@
         <v>79</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>264</v>
+        <v>79</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>351</v>
+        <v>79</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>352</v>
+        <v>79</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>79</v>
@@ -6311,13 +6361,13 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>347</v>
+        <v>322</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>79</v>
@@ -6326,27 +6376,27 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>79</v>
+        <v>326</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>354</v>
+        <v>79</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>355</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>356</v>
+        <v>328</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>356</v>
+        <v>328</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6354,7 +6404,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>89</v>
@@ -6369,17 +6419,15 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>357</v>
+        <v>171</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>358</v>
+        <v>172</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>79</v>
@@ -6428,7 +6476,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>356</v>
+        <v>174</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6437,16 +6485,16 @@
         <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>361</v>
+        <v>79</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>362</v>
+        <v>175</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>79</v>
@@ -6455,26 +6503,26 @@
         <v>79</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>363</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>364</v>
+        <v>329</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>364</v>
+        <v>329</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>79</v>
@@ -6486,16 +6534,16 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>357</v>
+        <v>134</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>365</v>
+        <v>178</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>366</v>
+        <v>179</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>360</v>
+        <v>151</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6545,25 +6593,25 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>364</v>
+        <v>181</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>361</v>
+        <v>140</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>362</v>
+        <v>175</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>79</v>
@@ -6572,47 +6620,51 @@
         <v>79</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>363</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>367</v>
+        <v>330</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>367</v>
+        <v>330</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>79</v>
+        <v>331</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J42" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>368</v>
+        <v>134</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>369</v>
+        <v>332</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>79</v>
       </c>
@@ -6660,42 +6712,42 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>367</v>
+        <v>334</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>370</v>
+        <v>132</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>371</v>
+        <v>79</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>372</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>373</v>
+        <v>335</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>373</v>
+        <v>335</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6703,7 +6755,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>89</v>
@@ -6718,16 +6770,18 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>368</v>
+        <v>195</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>374</v>
+        <v>336</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>375</v>
+        <v>337</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>79</v>
       </c>
@@ -6751,13 +6805,13 @@
         <v>79</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>79</v>
+        <v>279</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>79</v>
+        <v>339</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>79</v>
+        <v>340</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>79</v>
@@ -6775,7 +6829,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>373</v>
+        <v>335</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6790,27 +6844,27 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>376</v>
+        <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>377</v>
+        <v>341</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>371</v>
+        <v>79</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>372</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>378</v>
+        <v>342</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>378</v>
+        <v>342</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6818,7 +6872,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>89</v>
@@ -6833,17 +6887,15 @@
         <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>379</v>
+        <v>344</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6892,10 +6944,10 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>378</v>
+        <v>342</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>89</v>
@@ -6907,27 +6959,27 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>79</v>
+        <v>346</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>381</v>
+        <v>347</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>382</v>
+        <v>79</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>383</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>384</v>
+        <v>348</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>384</v>
+        <v>348</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6938,7 +6990,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>79</v>
@@ -6950,16 +7002,16 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>385</v>
+        <v>349</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>386</v>
+        <v>350</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>387</v>
+        <v>351</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7009,13 +7061,13 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>384</v>
+        <v>348</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>79</v>
@@ -7027,13 +7079,13 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>388</v>
+        <v>352</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>389</v>
+        <v>79</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7041,10 +7093,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>390</v>
+        <v>353</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>390</v>
+        <v>353</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7067,16 +7119,16 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>391</v>
+        <v>354</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>392</v>
+        <v>355</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>393</v>
+        <v>356</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>394</v>
+        <v>357</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7126,7 +7178,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>390</v>
+        <v>353</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7141,27 +7193,27 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>395</v>
+        <v>358</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>396</v>
+        <v>359</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>79</v>
+        <v>360</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>397</v>
+        <v>361</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>398</v>
+        <v>362</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>398</v>
+        <v>362</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7172,7 +7224,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>79</v>
@@ -7184,16 +7236,16 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>399</v>
+        <v>195</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>400</v>
+        <v>363</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>400</v>
+        <v>364</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>401</v>
+        <v>365</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7219,13 +7271,13 @@
         <v>79</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>79</v>
+        <v>279</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>79</v>
+        <v>366</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>79</v>
+        <v>367</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>79</v>
@@ -7243,13 +7295,13 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>398</v>
+        <v>362</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>79</v>
@@ -7261,24 +7313,24 @@
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>402</v>
+        <v>368</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>79</v>
+        <v>369</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>79</v>
+        <v>370</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7286,7 +7338,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>89</v>
@@ -7301,15 +7353,17 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>308</v>
+        <v>372</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>404</v>
+        <v>373</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7358,7 +7412,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7367,33 +7421,33 @@
         <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>101</v>
+        <v>376</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>406</v>
+        <v>377</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>407</v>
+        <v>79</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>79</v>
+        <v>378</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>408</v>
+        <v>379</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>408</v>
+        <v>379</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7416,15 +7470,17 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>175</v>
+        <v>372</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>176</v>
+        <v>380</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>79</v>
@@ -7473,7 +7529,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>178</v>
+        <v>379</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7482,16 +7538,16 @@
         <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>79</v>
+        <v>376</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>179</v>
+        <v>377</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
@@ -7500,26 +7556,26 @@
         <v>79</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>79</v>
+        <v>378</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>409</v>
+        <v>382</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>409</v>
+        <v>382</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>79</v>
@@ -7528,20 +7584,18 @@
         <v>79</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>134</v>
+        <v>383</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>182</v>
+        <v>384</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -7590,78 +7644,74 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>185</v>
+        <v>382</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>179</v>
+        <v>385</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>79</v>
+        <v>386</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>79</v>
+        <v>387</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>410</v>
+        <v>388</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>410</v>
+        <v>388</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>316</v>
+        <v>79</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>134</v>
+        <v>383</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>317</v>
+        <v>389</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>79</v>
       </c>
@@ -7709,42 +7759,42 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>319</v>
+        <v>388</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>79</v>
+        <v>391</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>132</v>
+        <v>392</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>79</v>
+        <v>386</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>79</v>
+        <v>387</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7752,7 +7802,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>89</v>
@@ -7767,15 +7817,17 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>412</v>
+        <v>349</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>413</v>
+        <v>394</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -7824,10 +7876,10 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>89</v>
@@ -7842,24 +7894,24 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>79</v>
+        <v>397</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>79</v>
+        <v>398</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7870,7 +7922,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>79</v>
@@ -7882,15 +7934,17 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>199</v>
+        <v>400</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -7915,13 +7969,13 @@
         <v>79</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>264</v>
+        <v>79</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>419</v>
+        <v>79</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>420</v>
+        <v>79</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>79</v>
@@ -7939,13 +7993,13 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>79</v>
@@ -7957,24 +8011,24 @@
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>353</v>
+        <v>403</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>422</v>
+        <v>79</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7997,15 +8051,17 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>199</v>
+        <v>406</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8030,13 +8086,13 @@
         <v>79</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>264</v>
+        <v>79</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>426</v>
+        <v>79</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>427</v>
+        <v>79</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>79</v>
@@ -8054,7 +8110,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8069,27 +8125,27 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>79</v>
+        <v>410</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>428</v>
+        <v>411</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>429</v>
+        <v>79</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>79</v>
+        <v>412</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8112,16 +8168,16 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>431</v>
+        <v>414</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>290</v>
+        <v>416</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8171,7 +8227,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8189,13 +8245,13 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>434</v>
+        <v>417</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>435</v>
+        <v>79</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
@@ -8203,21 +8259,21 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>437</v>
+        <v>79</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>79</v>
@@ -8229,17 +8285,15 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>438</v>
+        <v>323</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>439</v>
+        <v>419</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>79</v>
@@ -8288,13 +8342,13 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>79</v>
@@ -8306,13 +8360,13 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>442</v>
+        <v>421</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>79</v>
+        <v>422</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>79</v>
@@ -8320,10 +8374,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>443</v>
+        <v>423</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>443</v>
+        <v>423</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8334,7 +8388,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>79</v>
@@ -8346,17 +8400,15 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>444</v>
+        <v>171</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>445</v>
+        <v>172</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>447</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>79</v>
@@ -8405,33 +8457,965 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL62" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AG57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH57" t="s" s="2">
+      <c r="AM62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G63" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
+      <c r="H63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO57" t="s" s="2">
+      <c r="AK63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO65" t="s" s="2">
         <v>79</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
@@ -664,7 +664,7 @@
     <t>Rp番号(剤グループ番号)についてのsystem値</t>
   </si>
   <si>
-    <t>ここで付番されたIDがRp番号であることを明示するためにOIDとして定義された。urn:oid:1.2.392.100495.20.3.81で固定される。</t>
+    <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
   </si>
   <si>
     <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
@@ -673,7 +673,7 @@
     <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.100495.20.3.81</t>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -798,7 +798,7 @@
     <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
+    <t>urn:oid:1.2.392.100495.20.3.11</t>
   </si>
   <si>
     <t>MedicationDispense.identifier:requestIdentifier.value</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
@@ -272,7 +272,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}mdd-1:いつ準備されたときにハンドドーバーができないとき / whenHandedOver cannot be before whenPrepared {whenHandedOver.empty() or whenPrepared.empty() or whenHandedOver &gt;= whenPrepared}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}mdd-1:いつ準備されたときにハンドドーバーができないとき / whenHandedOver cannot be before whenPrepared {whenHandedOver.empty() or whenPrepared.empty() or whenHandedOver &gt;= whenPrepared}</t>
   </si>
   <si>
     <t>Event</t>
@@ -313,16 +313,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -448,7 +448,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -591,22 +591,22 @@
     <t>MedicationDispense.identifier.use</t>
   </si>
   <si>
-    <t>通常|公式|温度|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>この識別子の目的。 / The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>アプリケーションは、識別子が一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>特定の使用のコンテキストが一連の識別子の中から選択される適切な識別子を許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>通常|公式|一時的|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>このidentifierの目的。 / The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>アプリケーションは、identifierが一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>既知の場合、この識別子の目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
+    <t>既知の場合、このidentifierの目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
@@ -628,22 +628,22 @@
 </t>
   </si>
   <si>
-    <t>識別子の説明 / Description of identifier</t>
-  </si>
-  <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>この要素は、識別子の一般的なカテゴリのみを扱います。識別子。システムに対応するコードに使用しないでください。一部の識別子は、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明な識別子を処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>識別子システムが不明な場合、ユーザーは識別子を使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierの説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、identifierの一般的なカテゴリのみを扱います。identifier。システムに対応するコードに使用しないでください。一部のidentifierは、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明なidentifierを処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
@@ -667,10 +667,10 @@
     <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
   </si>
   <si>
-    <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+    <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
@@ -722,7 +722,7 @@
     <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
   </si>
   <si>
-    <t>識別子が使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>Identifier.period</t>
@@ -747,10 +747,10 @@
     <t>IDを発行した組織（単なるテキストである可能性があります） / Organization that issued id (may be just text)</t>
   </si>
   <si>
-    <t>識別子を発行/管理する組織。 / Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>識別子は、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+    <t>identifierを発行/管理する組織。 / Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>identifierは、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
   </si>
   <si>
     <t>Identifier.assigner</t>
@@ -774,7 +774,7 @@
     <t>薬剤をオーダする単位としての処方箋に対するID。原則として調剤の基となったMedicationRequestのIDを設定する。</t>
   </si>
   <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません。 / This is a business identifier, not a resource identifier.</t>
   </si>
   <si>
     <t>MedicationDispense.identifier:requestIdentifier.id</t>
@@ -792,7 +792,7 @@
     <t>MedicationDispense.identifier:requestIdentifier.system</t>
   </si>
   <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
   </si>
   <si>
     <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
@@ -807,10 +807,10 @@
     <t>一意の値 / The value that is unique</t>
   </si>
   <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>MedicationDispense.identifier:requestIdentifier.period</t>
@@ -1191,7 +1191,7 @@
     <t>使用状況によって、これがどのような量であるか、したがってどのような単位を使用できるかが定義される場合がかなりある。使用状況によっては、比較演算子の値も制限される場合がある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
@@ -1455,7 +1455,7 @@
 DetectedIssue リソースへの参照。</t>
   </si>
   <si>
-    <t>この要素には、意思決定支援システムまたは臨床医によって特定された検出された問題を含めることができ、問題に対処するために取られた手順に関する情報を含めることができます。 / This element can include a detected issue that has been identified either by a decision support system or by a clinician and may include information on the steps that were taken to address the issue.</t>
+    <t>この要素には、意思決定支援システムまたは臨床医によって特定された検出された問題を含めることができ、問題に対処するために取られたプロシジャー（処置等）に関する情報を含めることができます。 / This element can include a detected issue that has been identified either by a decision support system or by a clinician and may include information on the steps that were taken to address the issue.</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ]/source[classCode=ALRT,moodCode=EVN].value</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2437" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2437" uniqueCount="467">
   <si>
     <t>Property</t>
   </si>
@@ -1191,14 +1191,13 @@
     <t>使用状況によって、これがどのような量であるか、したがってどのような単位を使用できるかが定義される場合がかなりある。使用状況によっては、比較演算子の値も制限される場合がある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
+    <t>.quantity</t>
+  </si>
+  <si>
+    <t>CombinedMedicationDispense.SupplyEvent.quantity</t>
+  </si>
+  <si>
+    <t>RXD-4-Actual Dispense Amount / RXD-5.1-Actual Dispense Units.code / RXD-5.3-Actual Dispense Units.name of coding system</t>
   </si>
   <si>
     <t>MedicationDispense.daysSupply</t>
@@ -1208,6 +1207,15 @@
   </si>
   <si>
     <t>タイミングとして表される投薬量。すなわち、XX日分、XX回分などの数量。</t>
+  </si>
+  <si>
+    <t>effectiveUseTime</t>
+  </si>
+  <si>
+    <t>TQ1.6 Timing/Quantity Segment Service Duration.+Prior to v2.5, ORC.7.3 Common Order Segment / Quantity/Timing / Duration component.  This is a formatted string, first character for the time unit (e.g., D=days), followed by the value.  For example, “D14” represents “14 days supply”+From v2.5 on, TQ1.6 Timing/Quantity Segment / Service Duration.  This is a CQ data type (&lt;Quantity (NM)&gt; ^ &lt;Units (CWE)&gt;), thus for days supply, assuming the unit of measure is “days”, the numeric value is TQ1.6.1 (…|14^+For backwards compatibility, ORC.7 was permitted through v2.6.  Both forms (field and segment) may be present in v2.5, v2.5.1, and v2.6</t>
   </si>
   <si>
     <t>MedicationDispense.whenPrepared</t>
@@ -1315,7 +1323,10 @@
 </t>
   </si>
   <si>
-    <t>薬の服用方法・服用した方法、または服用すべき方法</t>
+    <t>患者が薬をどのように使用するか、または介護者が投与する / How the medication is to be used by the patient or administered by the caregiver</t>
+  </si>
+  <si>
+    <t>患者が薬をどのように使用するかを示します。 / Indicates how the medication is to be used by the patient.</t>
   </si>
   <si>
     <t>投与または速度が行政期間全体で変化することを目的としている場合（例：用量処方の先細り）、さまざまな用量/レートを伝えるために投与量の指示の複数のインスタンスを提供する必要があります。@@ -1823,7 +1834,7 @@
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="73.296875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="94.375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7421,22 +7432,22 @@
         <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ48" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL48" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AK48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL48" t="s" s="2">
+      <c r="AM48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>378</v>
@@ -7538,16 +7549,16 @@
         <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>376</v>
+        <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
@@ -7556,15 +7567,15 @@
         <v>79</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7587,13 +7598,13 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7644,7 +7655,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7662,24 +7673,24 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7702,13 +7713,13 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7759,7 +7770,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7774,27 +7785,27 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7820,10 +7831,10 @@
         <v>349</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>305</v>
@@ -7876,7 +7887,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7894,24 +7905,24 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7934,13 +7945,13 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>305</v>
@@ -7993,7 +8004,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8011,13 +8022,13 @@
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
@@ -8025,10 +8036,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8051,16 +8062,16 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8110,7 +8121,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8125,10 +8136,10 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>79</v>
@@ -8137,15 +8148,15 @@
         <v>79</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8168,16 +8179,16 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8227,7 +8238,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8245,7 +8256,7 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
@@ -8259,10 +8270,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8288,10 +8299,10 @@
         <v>323</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8342,7 +8353,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8360,13 +8371,13 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>79</v>
@@ -8374,10 +8385,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8489,10 +8500,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8606,10 +8617,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8725,10 +8736,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8751,13 +8762,13 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8808,7 +8819,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>89</v>
@@ -8826,7 +8837,7 @@
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>79</v>
@@ -8840,10 +8851,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8869,10 +8880,10 @@
         <v>195</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8902,28 +8913,28 @@
         <v>279</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF61" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -8947,18 +8958,18 @@
         <v>79</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8984,10 +8995,10 @@
         <v>195</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9017,28 +9028,28 @@
         <v>279</v>
       </c>
       <c r="Y62" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF62" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9056,13 +9067,13 @@
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -9070,10 +9081,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9096,13 +9107,13 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>305</v>
@@ -9155,7 +9166,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9173,13 +9184,13 @@
         <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>79</v>
@@ -9187,14 +9198,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9213,16 +9224,16 @@
         <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9272,7 +9283,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9290,7 +9301,7 @@
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>79</v>
@@ -9304,10 +9315,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9330,16 +9341,16 @@
         <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9389,7 +9400,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9407,7 +9418,7 @@
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
@@ -1214,7 +1214,7 @@
   <si>
     <t>TQ1.6 Timing/Quantity Segment Service Duration. Prior to v2.5, ORC.7.3 Common Order Segment / Quantity/Timing / Duration component.  This is a formatted string, first character for the time unit (e.g., D=days), followed by the value.  For example, “D14” represents “14 days supply”-From v2.5 on, TQ1.6 Timing/Quantity Segment / Service Duration.  This is a CQ data type (&lt;Quantity (NM)&gt; ^ &lt;Units (CWE)&gt;), thus for days supply, assuming the unit of measure is “days”, the numeric value is TQ1.6.1 (…|14^+From v2.5 on, TQ1.6 Timing/Quantity Segment / Service Duration.  This is a CQ data type (Quantity (NM) ^ Units (CWE)), thus for days supply, assuming the unit of measure is “days”, the numeric value is TQ1.6.1 (…|14^ For backwards compatibility, ORC.7 was permitted through v2.6.  Both forms (field and segment) may be present in v2.5, v2.5.1, and v2.6</t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
@@ -272,7 +272,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}mdd-1:いつ準備されたときにハンドドーバーができないとき / whenHandedOver cannot be before whenPrepared {whenHandedOver.empty() or whenPrepared.empty() or whenHandedOver &gt;= whenPrepared}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}mdd-1:いつ準備されたときにハンドドーバーができないとき / whenHandedOver cannot be before whenPrepared {whenHandedOver.empty() or whenPrepared.empty() or whenHandedOver &gt;= whenPrepared}</t>
   </si>
   <si>
     <t>Event</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
@@ -1795,17 +1795,17 @@
   <dimension ref="A1:AO65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="53.73046875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="48.12109375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.3125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.06640625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="41.2578125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="13.984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="246.64453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="211.453125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1814,26 +1814,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="197.484375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="71.296875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="46.84375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="169.3046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="40.16015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="73.296875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="245.42578125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="62.83984375" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
@@ -1090,10 +1090,10 @@
 </t>
   </si>
   <si>
-    <t>演奏していた個人 / Individual who was performing</t>
-  </si>
-  <si>
-    <t>アクションを実行したデバイス、開業医など。俳優は薬のディスペンサーであると想定されるべきです。 / The device, practitioner, etc. who performed the action.  It should be assumed that the actor is the dispenser of the medication.</t>
+    <t>調剤をした個人 / Individual who was performing</t>
+  </si>
+  <si>
+    <t>アクションを実行したデバイス、個人など。調剤した薬のディスペンサーであると想定されるべきです。 / The device, practitioner, etc. who performed the action.  It should be assumed that the actor is the dispenser of the medication.</t>
   </si>
   <si>
     <t>Event.performer.actor</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
@@ -367,7 +367,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -646,7 +646,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -740,7 +740,7 @@
     <t>MedicationDispense.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -872,7 +872,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(DetectedIssue)</t>
+Reference(DetectedIssue|4.0.1)</t>
   </si>
   <si>
     <t>調剤が実行されなかった理由</t>
@@ -887,7 +887,7 @@
     <t>ディスペンスが実行されなかった理由を説明するコード。 / A code describing why a dispense was not performed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -911,7 +911,7 @@
     <t>分配された薬がどこで消費または投与されると予想されるコード。 / A code describing where the dispensed medication is expected to be consumed or administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-category|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication dispense"].value</t>
@@ -1003,7 +1003,7 @@
     <t>MedicationDispense.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1077,7 +1077,7 @@
     <t>個人が薬物療法を調剤する上で果たした役割を説明するコード。 / A code describing the role an individual played in dispensing a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function|4.0.1</t>
   </si>
   <si>
     <t>participation[typeCode=PRF].functionCode</t>
@@ -1455,7 +1455,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue)
+    <t xml:space="preserve">Reference(DetectedIssue|4.0.1)
 </t>
   </si>
   <si>
@@ -1475,7 +1475,7 @@
     <t>MedicationDispense.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2437" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2436" uniqueCount="466">
   <si>
     <t>Property</t>
   </si>
@@ -1411,16 +1411,13 @@
     <t>MedicationDispense.substitution.reason</t>
   </si>
   <si>
-    <t>置換が実施された理由</t>
-  </si>
-  <si>
-    <t>治療継続性確保のため、FP:処方方針、 OS: 在庫欠品、  RR:代替えを義務付けまたは禁止する規制要件に従った</t>
-  </si>
-  <si>
-    <t>別の薬物療法が処方されたものから置き換える（またはすべきではない）理由を説明するコード化された概念。 / A coded concept describing the reason that a different medication should (or should not) be substituted from what was prescribed.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-SubstanceAdminSubstitutionReason</t>
+    <t>置換が実施された（あるいは、されなかった）理由</t>
+  </si>
+  <si>
+    <t>【JP Core仕様】置換が実施された、あるいは実施されなかった理由を示す。令和6年保険改訂により、処方箋上で長期収載医薬品の変更不可が指定されている場合は「医療上の必要性がある」または「患者希望による」のいずれかを指定する。</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationSubstitutionProhibitionReason_VS</t>
   </si>
   <si>
     <t>.reasonCode</t>
@@ -1820,7 +1817,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="169.3046875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.2890625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -9025,13 +9022,11 @@
         <v>79</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="Y62" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y62" s="2"/>
+      <c r="Z62" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>79</v>
@@ -9067,13 +9062,13 @@
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -9081,10 +9076,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9107,13 +9102,13 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>305</v>
@@ -9166,7 +9161,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9184,13 +9179,13 @@
         <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>79</v>
@@ -9198,14 +9193,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9224,16 +9219,16 @@
         <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9283,7 +9278,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9301,7 +9296,7 @@
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>79</v>
@@ -9315,10 +9310,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9341,16 +9336,16 @@
         <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9400,7 +9395,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9418,7 +9413,7 @@
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
@@ -1155,7 +1155,7 @@
     <t>実行される調剤イベントのタイプを示す。たとえば、トライアルフィル、トライアルの完了、部分フィル、緊急フィル、サンプルなどである。</t>
   </si>
   <si>
-    <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、コーディングを直接使用して、テキスト、コーディング、翻訳、および要素間の関係とpre-coordinationとpost-coordinationの用語関係を管理するための独自の構造を提供する必要がある。</t>
+    <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、`Coding`を直接使用して、テキスト、`Coding`、翻訳、および要素間の関係とpre-coordinationとpost-coordinationの用語関係を管理するための独自の構造を提供する必要がある。</t>
   </si>
   <si>
     <t>実行される分配イベントのタイプを示します。たとえば、試行充填、試行の完了、部分充填、緊急充填、サンプルなど。 / Indicates the type of dispensing event that is performed. For example, Trial Fill, Completion of Trial, Partial Fill, Emergency Fill, Samples, etc.</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationdispense-injection.xlsx
@@ -508,7 +508,7 @@
   <si>
     <t>このインスタンスが外部から参照されるために使われるIDである。処方箋全体としてのIDとしては使用しない。  
 処方箋内で同一の用法をまとめて表記されるRp番号はこのIdentifier elementの別スライスで表現する。それ以外に任意のIDを付与してもよい。  
-このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバからサーバに転送されたとしても固定のものとして存続する。</t>
+このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバーからサーバーに転送されたとしても固定のものとして存続する。</t>
   </si>
   <si>
     <t>これは業務IDであって、リソースに対するIDではない。</t>
@@ -1304,7 +1304,7 @@
   </si>
   <si>
     <t>構造化された注釈（アノテーション）を持たないシステムの場合、作成者や時間なしで単一の注釈を簡単に伝達できる。情報を変更する可能性があるため、この要素をナラティブに含める必要がある場合がある。  
-*注釈は、計算機処理れきる「変更」情報を伝達するために使用されるべきではない*。 （ユーザの行動を強制することはほとんど不可能であるため、これはSHOULDとする）。</t>
+*注釈は、計算機処理れきる「変更」情報を伝達するために使用されるべきではない*。 （ユーザーの行動を強制することはほとんど不可能であるため、これはSHOULDとする）。</t>
   </si>
   <si>
     <t>Event.note</t>
